--- a/content/tz-lager-v-kitae-s-izucheniem-kitayskogo.xlsx
+++ b/content/tz-lager-v-kitae-s-izucheniem-kitayskogo.xlsx
@@ -19,6 +19,7 @@
     <sheet name="Ссылки" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Проверки" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Оговорки" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Правка языка" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -530,7 +531,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Лагерь в Китае с изучением китайского — это не курсы для детей. Родитель платит не за уроки, а за то, что за ребёнка отвечают круглые сутки: уроков в смене несколько часов в день, а всё остальное время тоже надо кому-то закрывать. Разбираем, чем лагерь отличается от языковой программы и от тура, сколько языка правда вырастет за смену, что спросить до оплаты и какие слова пригодятся в быту.</t>
+          <t>Лагерь в Китае с изучением китайского — это не курсы для детей. Родитель платит не за уроки, а за то, что за ребёнка отвечают круглые сутки: уроков в смене несколько часов в день, а всё остальное время рядом тоже должен быть взрослый. Разбираем, чем лагерь отличается от языковой программы и от тура, сколько языка правда вырастет за смену, что спросить до оплаты и какие слова пригодятся в быту.</t>
         </is>
       </c>
     </row>
@@ -602,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>39 721 знак (лимит ≈ 50 000)</t>
+          <t>40 048 знаков (лимит ≈ 50 000)</t>
         </is>
       </c>
     </row>
@@ -626,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>26,3 % (норма 26–31 %)</t>
+          <t>27,0 % (норма 26–31 %)</t>
         </is>
       </c>
     </row>
@@ -638,7 +639,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>36,5 %; FAQ на 64,0 %</t>
+          <t>36,8 %; FAQ на 64,3 %</t>
         </is>
       </c>
     </row>
@@ -982,7 +983,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>39 721 знак</t>
+          <t>40 048 знаков</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1007,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Инфографика 26,3 %, «Из личного опыта» 36,5 %, FAQ 64,0 %</t>
+          <t>Инфографика 27,0 %, «Из личного опыта» 36,8 %, FAQ 64,3 %</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1031,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Не найдено</t>
+          <t>После правки языка не осталось. См. лист «Правка языка»</t>
         </is>
       </c>
     </row>
@@ -1164,6 +1165,287 @@
       <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Самая недооценённая строка в таблице вопросов. Если всю смену рядом только русскоязычные, китайский останется внутри уроков. Это тот же механизм, что у взрослых на языковых программах — и ровно то, чем закрыт ключ «лагерь в Китае для русских»</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Восемнадцать мест, переписанных после первой сдачи</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Было</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Стало</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Почему</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>«Уровень за смену не прыгнет… но вырастает смелость говорить, и это честно ценнее»</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>«Уровень за смену почти не изменится: две-три недели для этого мало. Зато ребёнок начинает говорить вслух, и дома это видно сразу»</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>«не прыгнет» — метафора на месте обычного глагола; «честно ценнее» — непонятно, ценнее чего</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>«Одним словом называют три разных продукта, и путаница тут стоит не денег, а разочарования. Разница не в качестве»</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>«Лагерь, языковую программу и тур часто называют одним словом. Но устроены они по-разному, и платите вы в каждом случае за разное. Плохих среди них нет»</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>«продукт» — жаргон; «путаница стоит разочарования» — нелогично, она стоит и денег тоже; про качество никто не говорил</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>«всё остальное время тоже надо кому-то закрывать» (в дескрипшене и в FAQ)</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>«за всё остальное время тоже кто-то должен отвечать»</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>«закрывать время» — жаргон</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>«Спрашивать про расселение не мелочно, это прямо про результат»</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>«Вопрос про расселение — не придирка: от него прямо зависит, заговорит ребёнок или нет»</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Обе конструкции натянутые</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>«Всё остальное время в рекламе не показывают, а стоит оно дороже» (подпись под инфографикой)</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>«Остальные часы не показывают — а ведь именно за них вы и платите»</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>«стоит дороже» — цифра, которую мы не проверяли</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>«язык набирается временем», «обещать скачок значило бы обманывать»</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>«язык требует времени», «обещать другое было бы обманом»</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Книжные обороты</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>«запоминаются намертво»</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>«запоминаются надолго»</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Метафора</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>«чтобы смена сработала на язык» (2 места, в тексте и в CTA)</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>«чтобы поездка дала язык», «чтобы после смены ребёнок правда заговорил»</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Жаргон</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>«мелочь, на которой подростки спотыкаются»</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>«мелочь, про которую лучше знать заранее»</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Метафора</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>«самая вероятная неприятность — и самая недодуманная»</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>«самое частое, что случается в поездке, — и то, о чём думают в последнюю очередь»</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>«недодуманная» — выдуманное слово</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>«зазвучит ли китайский вообще»</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>«заговорит ли ребёнок по-китайски вообще»</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Метафора</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>«проверяют на своём году» (2 места)</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>«проверяют перед самой поездкой», «уточняется перед поездкой»</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Непонятный оборот</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>«от этого зависит язык» (строка таблицы)</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>«от этого зависит, заговорит ли он»</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Расплывчато</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>«Всё остальное это сон, еда, дорога»</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>«Всё остальное — это сон, еда, дорога»</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Пропущенное тире</t>
         </is>
       </c>
     </row>

--- a/content/tz-lager-v-kitae-s-izucheniem-kitayskogo.xlsx
+++ b/content/tz-lager-v-kitae-s-izucheniem-kitayskogo.xlsx
@@ -20,6 +20,7 @@
     <sheet name="Проверки" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Оговорки" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="Правка языка" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Правка языка 2" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -531,7 +532,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Лагерь в Китае с изучением китайского — это не курсы для детей. Родитель платит не за уроки, а за то, что за ребёнка отвечают круглые сутки: уроков в смене несколько часов в день, а всё остальное время рядом тоже должен быть взрослый. Разбираем, чем лагерь отличается от языковой программы и от тура, сколько языка правда вырастет за смену, что спросить до оплаты и какие слова пригодятся в быту.</t>
+          <t>Лагерь в Китае с изучением китайского — это не курсы для детей. Родитель платит не за уроки, а за то, что за ребёнка отвечают круглые сутки: уроков в смене несколько часов в день, а всё остальное время рядом тоже должен быть взрослый. Разбираем, чем лагерь отличается от языковой программы и от тура, насколько вырастет уровень языка за смену, что спросить до оплаты и какие слова пригодятся в быту.</t>
         </is>
       </c>
     </row>
@@ -543,7 +544,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Чем лагерь в Китае отличается от языковых курсов и тура, сколько языка вырастет за смену, что спросить про присмотр и какие слова нужны в общежитии.</t>
+          <t>Чем лагерь в Китае отличается от языковых курсов и тура, насколько вырастет уровень языка за смену, что спросить про присмотр и какие слова нужны в общежитии.</t>
         </is>
       </c>
     </row>
@@ -603,7 +604,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>40 048 знаков (лимит ≈ 50 000)</t>
+          <t>40 251 знак (лимит ≈ 50 000)</t>
         </is>
       </c>
     </row>
@@ -627,7 +628,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>27,0 % (норма 26–31 %)</t>
+          <t>26,7 % (норма 26–31 %)</t>
         </is>
       </c>
     </row>
@@ -639,7 +640,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>36,8 %; FAQ на 64,3 %</t>
+          <t>36,8 %; FAQ на 64,1 %</t>
         </is>
       </c>
     </row>
@@ -983,7 +984,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>40 048 знаков</t>
+          <t>40 251 знак</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1008,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Инфографика 27,0 %, «Из личного опыта» 36,8 %, FAQ 64,3 %</t>
+          <t>Инфографика 26,7 %, «Из личного опыта» 36,8 %, FAQ 64,1 %</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1191,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Восемнадцать мест, переписанных после первой сдачи</t>
+          <t>Первый проход: восемнадцать мест</t>
         </is>
       </c>
     </row>
@@ -1446,6 +1447,219 @@
       <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Пропущенное тире</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Второй проход: ещё девять мест</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Было</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Стало</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Почему</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>«сосед по комнате, отбой, стирка, отпроситься» (в «Коротко»)</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>«про соседа по комнате, про отбой, про стирку и про то, как отпроситься»</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Три существительных и глагол в одном перечислении</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>«Вопрос про расселение — не придирка: от него прямо зависит, заговорит ребёнок или нет. И нормальный организатор отвечает на такой вопрос сразу: расселение он всё равно планирует заранее»</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>«Поэтому про расселение спросить стоит обязательно. И нормальный организатор ответит сразу — он всё равно сам решает, кого с кем поселить, ещё до приезда детей»</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Два двоеточия подряд, а мысль про «заговорит или нет» уже сказана в предыдущей фразе</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>H2 «Сколько языка вырастет за смену»</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>H2 «Что будет с уровнем языка за смену»</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Растёт не «язык», а уровень</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>«Честный ответ: уровень заметно не поднимется. Две-три недели для этого мало: язык требует времени»</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>«Отвечу честно: за одну смену уровень почти не изменится. Две-три недели — слишком мало. Чтобы уровень вырос, нужны месяцы регулярных занятий»</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>«Честный ответ» и «язык требует времени» — обороты ни о чём. Заменены на то, что можно проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>«Зато меняется другое, и это не утешительный приз»</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>«Зато меняется отношение к языку»</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>«Другое» — что именно? Названо прямо</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>«С полного нуля поездка превращается в экскурсию с кружком» (3 места)</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>«Если ребёнок едет совсем без языка, получится поездка с впечатлениями и парой занятий»</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>«Экскурсия с кружком» — придуманный образ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>«продавать её как языковую программу нечестно» (2 места)</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>«называть её языковой программой нечестно»</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Мы ничего не продаём — мы называем вещи своими именами</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>FAQ «Сколько китайского вырастет за одну смену?»</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>FAQ «Насколько вырастет уровень китайского за одну смену?»</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>То же, что с H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>«И обратная сторона, о которой стоит подумать заранее»</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>«Есть и обратная сторона, о которой стоит подумать заранее»</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Фраза без сказуемого</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>МЕТА-ТЕГИ</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>В дескрипшене, в og/twitter и в JSON-LD «сколько языка вырастет за смену» заменено на «насколько вырастет уровень языка за смену»</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Та же ошибка, что в заголовке раздела</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2295,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Сколько языка вырастет за смену</t>
+          <t>Что будет с уровнем языка за смену</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
